--- a/tests/reports/neuro_assistant_test_report.xlsx
+++ b/tests/reports/neuro_assistant_test_report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,12 @@
       <b val="1"/>
       <color rgb="0038761D"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00990000"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +62,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -99,6 +108,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -517,7 +529,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:38</t>
+          <t>21.05.2026 21:34:50</t>
         </is>
       </c>
     </row>
@@ -529,7 +541,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:49</t>
+          <t>21.05.2026 21:35:36</t>
         </is>
       </c>
     </row>
@@ -540,7 +552,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11.3119</v>
+        <v>45.2602</v>
       </c>
     </row>
     <row r="7">
@@ -550,7 +562,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -560,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -570,7 +582,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -581,7 +593,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Успешно</t>
+          <t>Есть ошибки</t>
         </is>
       </c>
     </row>
@@ -596,23 +608,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,16 +746,16 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:38</t>
+          <t>21.05.2026 21:34:51</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:38</t>
+          <t>21.05.2026 21:34:51</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.0262</v>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
     </row>
@@ -784,28 +796,32 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: Internal Server Error</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:38</t>
+          <t>21.05.2026 21:34:51</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:41</t>
+          <t>21.05.2026 21:34:54</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>2.924</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
+        <v>2.2895</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -844,28 +860,32 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: Internal Server Error</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:41</t>
+          <t>21.05.2026 21:34:54</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:42</t>
+          <t>21.05.2026 21:34:57</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.4369</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
+        <v>3.0726</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -904,28 +924,32 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: Internal Server Error</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:42</t>
+          <t>21.05.2026 21:34:57</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:42</t>
+          <t>21.05.2026 21:34:59</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
+        <v>2.045</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -964,28 +988,32 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: Internal Server Error</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:42</t>
+          <t>21.05.2026 21:34:59</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:43</t>
+          <t>21.05.2026 21:35:01</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.3254</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
+        <v>2.0262</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1024,28 +1052,32 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: Internal Server Error</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:43</t>
+          <t>21.05.2026 21:35:01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:44</t>
+          <t>21.05.2026 21:35:03</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.4411</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>2.0404</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1084,28 +1116,32 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: {"detail":"Ошибка загрузки менеджеров: [WinError 10061] Подключение не установлено, т.к. конечный компьютер отверг запрос на подключение"}</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:44</t>
+          <t>21.05.2026 21:35:03</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:44</t>
+          <t>21.05.2026 21:35:06</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
+        <v>3.1008</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1144,28 +1180,32 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: {"detail":"Ошибка загрузки сотрудников: [WinError 10061] Подключение не установлено, т.к. конечный компьютер отверг запрос на подключение"}</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:44</t>
+          <t>21.05.2026 21:35:06</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:09</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.4334</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>3.0768</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1204,28 +1244,32 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>HTTP 500: {"detail":"Ошибка загрузки заказов: [WinError 10061] Подключение не установлено, т.к. конечный компьютер отверг запрос на подключение"}</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:09</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:13</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.4419</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>3.9515</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Код ответа не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1280,16 +1324,16 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:13</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:13</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.0017</v>
+        <v>0.0032</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
     </row>
@@ -1336,28 +1380,32 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>intent = error</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:45</t>
+          <t>21.05.2026 21:35:13</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:46</t>
+          <t>21.05.2026 21:35:15</t>
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.4688</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
+        <v>2.0528</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1402,28 +1450,32 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>intent = error</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:46</t>
+          <t>21.05.2026 21:35:15</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:46</t>
+          <t>21.05.2026 21:35:17</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.4442</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
+        <v>2.0275</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1468,28 +1520,32 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>intent = error</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:46</t>
+          <t>21.05.2026 21:35:17</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:47</t>
+          <t>21.05.2026 21:35:19</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.4467</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
+        <v>2.0363</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1534,28 +1590,32 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>intent = error</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:47</t>
+          <t>21.05.2026 21:35:19</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:47</t>
+          <t>21.05.2026 21:35:21</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.4384</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>2.0429</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1600,28 +1660,32 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>intent = error</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:47</t>
+          <t>21.05.2026 21:35:21</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:24</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.4589</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>3.0521</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1666,28 +1730,32 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>parameters.action = None</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:24</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:26</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.4446</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>2.0433</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1732,28 +1800,32 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>parameters.action = None</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:26</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:28</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.4386</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>2.0339</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1798,28 +1870,32 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>parameters.action = None</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:48</t>
+          <t>21.05.2026 21:35:28</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:49</t>
+          <t>21.05.2026 21:35:30</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.4468</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+        <v>2.0292</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1864,28 +1940,32 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Проверка выполнена успешно</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Успешно</t>
+          <t>parameters.action = None</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:49</t>
+          <t>21.05.2026 21:35:30</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>07.05.2026 17:40:49</t>
+          <t>21.05.2026 21:35:32</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>2.0566</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1893,30 +1973,100 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>Создание confirm_action для Telegram-рассылки</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Проверяется функция: «Создание confirm_action для Telegram-рассылки». Тест относится к модулю «Pending action parser». Выполняется POST-запрос к endpoint «/api/voice/text». Система должна вернуть корректный ответ и подтвердить работоспособность проверяемой функции. Дополнительно проверяется значение поля «parameters.action»: ожидаемое значение — «send_mailing».</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Pending action parser</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>/api/voice/text</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>{
+  "text": "Надо сделать рассылку"
+}</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 200, поле parameters.action = send_mailing</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>parameters.action = None</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>21.05.2026 21:35:32</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>21.05.2026 21:35:35</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>2.9975</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Значение поля не совпадает с ожидаемым</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>Генерация PDF-файла</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Проверяется функция: «Генерация PDF-файла». Тест относится к модулю «PDF API». Выполняется POST-запрос к endpoint «/api/pdf/download». Система должна вернуть корректный ответ и подтвердить работоспособность проверяемой функции.</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>PDF API</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>/api/pdf/download</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>{
   "recognized_text": "Тестовая команда",
@@ -1928,35 +2078,35 @@
 }</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Получен бинарный файл</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Размер файла: 48771 байт</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Размер файла: 48774 байт</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Успешно</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>07.05.2026 17:40:49</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>07.05.2026 17:40:49</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0.0623</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>21.05.2026 21:35:35</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>21.05.2026 21:35:36</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
